--- a/zabbix/clients-module/test/fixtures/export.xlsx
+++ b/zabbix/clients-module/test/fixtures/export.xlsx
@@ -2137,7 +2137,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">The host's name in Zabbix, filled in on export so you can tell the rows apart. Not read on import: ElasticPro names new hosts from the client and the roles (Acme-ES-Data-Hot-1).</t>
+          <t xml:space="preserve">Empty: ElasticPro names a new host from the client and its roles (Acme-ES-Data-Hot-1). Give one to keep your own: letters, digits, spaces, dots, dashes and underscores, unique in Zabbix; no later save changes it. On an existing server a different name renames the host (its history stays); an empty cell keeps the name it has. Export fills in every host's name.
+Example: acme-edge-01</t>
         </r>
       </text>
     </comment>
@@ -2417,7 +2418,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Leave it empty: ElasticPro names each host from the client and its roles (Acme-ES-Data-Hot-1). On export it shows the name the host has in Zabbix; it is not read back.</t>
+          <t xml:space="preserve">Leave it empty and ElasticPro names the host from the client and its roles (Acme-ES-Data-Hot-1). Give one to keep your own, as Acme's 10.10.0.21 does: letters, digits, spaces, dots, dashes and underscores, unique in Zabbix.</t>
         </r>
       </text>
     </comment>
